--- a/AAII_Financials/Yearly/LGMMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LGMMY_YR_FIN.xlsx
@@ -1530,10 +1530,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>252100</v>
+        <v>222300</v>
       </c>
       <c r="E43" s="3">
-        <v>786200</v>
+        <v>775500</v>
       </c>
       <c r="F43" s="3">
         <v>318100</v>
@@ -1611,10 +1611,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1225100</v>
+        <v>1195300</v>
       </c>
       <c r="E46" s="3">
-        <v>1255100</v>
+        <v>1244400</v>
       </c>
       <c r="F46" s="3">
         <v>716300</v>
@@ -1773,10 +1773,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>23002700</v>
+        <v>23032500</v>
       </c>
       <c r="E52" s="3">
-        <v>18483600</v>
+        <v>18494300</v>
       </c>
       <c r="F52" s="3">
         <v>20008600</v>
